--- a/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-at-scheduling-healthcareservice.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-at-scheduling-healthcareservice.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:33:33+00:00</t>
+    <t>2026-08-18T09:10:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,7 +451,7 @@
     <t>cancellationPolicy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
 </t>
   </si>
   <si>
@@ -556,7 +556,7 @@
     <t>HealthcareService.offeredIn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -620,7 +620,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -1284,7 +1284,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.1875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.8203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1299,7 +1299,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.7578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
